--- a/data/ams_weekly_data/Audio_Array/ads_report_week17.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week17.xlsx
@@ -12691,7 +12691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12853,19 +12853,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28994</v>
+        <v>22625</v>
       </c>
       <c r="E5" t="n">
-        <v>223</v>
+        <v>174</v>
       </c>
       <c r="F5" t="n">
-        <v>4413.96</v>
+        <v>3444.338824107375</v>
       </c>
       <c r="G5" t="n">
-        <v>23805.09</v>
+        <v>18575.79037833833</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -12877,28 +12877,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
+          <t>Audio Array-B0B4DPX2J2-Condenser AM C1-SBV-KT-Exact/Phrase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14369</v>
+        <v>6369</v>
       </c>
       <c r="E6" t="n">
-        <v>98</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>945.3766666666667</v>
+        <v>969.6211758926249</v>
       </c>
       <c r="G6" t="n">
-        <v>8994.35</v>
+        <v>5229.299621661675</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -12915,23 +12915,23 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0B4G8PH2P</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14369</v>
+        <v>3982</v>
       </c>
       <c r="E7" t="n">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="F7" t="n">
-        <v>945.3766666666667</v>
+        <v>261.975319393795</v>
       </c>
       <c r="G7" t="n">
-        <v>8994.35</v>
+        <v>2492.443273745822</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -12948,23 +12948,23 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14369</v>
+        <v>9066</v>
       </c>
       <c r="E8" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="F8" t="n">
-        <v>945.3766666666667</v>
+        <v>596.4818933764792</v>
       </c>
       <c r="G8" t="n">
-        <v>8994.35</v>
+        <v>5674.951695822197</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -12976,28 +12976,28 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Audio Array-B0BPLZ5CGV-AI 04 Audio Interface-SBV -PT</t>
+          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>54218</v>
+        <v>29042</v>
       </c>
       <c r="E9" t="n">
-        <v>375</v>
+        <v>198</v>
       </c>
       <c r="F9" t="n">
-        <v>4055.86</v>
+        <v>1910.747305897211</v>
       </c>
       <c r="G9" t="n">
-        <v>18300.84</v>
+        <v>18178.92342466309</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -13009,28 +13009,28 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase</t>
+          <t>Audio Array-B0BLJVJ2GN-AA 05 Suspension-SB-PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15729</v>
+        <v>1017</v>
       </c>
       <c r="E10" t="n">
-        <v>117</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>1441.79</v>
+        <v>66.92548133251506</v>
       </c>
       <c r="G10" t="n">
-        <v>21605.95</v>
+        <v>636.7316057688894</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -13042,28 +13042,28 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Audio Array-B0DXFPM4N2-Studio Monitor- SBV-CT</t>
+          <t>Audio Array-B0BPLZ5CGV-AI 04 Audio Interface-SBV -PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B0DXFPM4N2</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>23825</v>
+        <v>50697</v>
       </c>
       <c r="E11" t="n">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="F11" t="n">
-        <v>1926.31</v>
+        <v>3744.050978284915</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>16606.77</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -13075,28 +13075,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-Condenser -SB-PT</t>
+          <t>Audio Array-B0BPLZ5CGV-AI 04 Audio Interface-SBV -PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0FG88HVQ8</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>23409.33333333333</v>
+        <v>3521</v>
       </c>
       <c r="E12" t="n">
-        <v>87.33333333333333</v>
+        <v>32</v>
       </c>
       <c r="F12" t="n">
-        <v>1452.846666666667</v>
+        <v>311.8090217150854</v>
       </c>
       <c r="G12" t="n">
-        <v>2287.29</v>
+        <v>1694.07</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -13108,28 +13108,28 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-Condenser -SB-PT</t>
+          <t>Audio Array-B0CKHVHVQ1-AM W45 Wireless-SBV-KT-Phrase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23409.33333333333</v>
+        <v>15729</v>
       </c>
       <c r="E13" t="n">
-        <v>87.33333333333333</v>
+        <v>117</v>
       </c>
       <c r="F13" t="n">
-        <v>1452.846666666667</v>
+        <v>1441.79</v>
       </c>
       <c r="G13" t="n">
-        <v>2287.29</v>
+        <v>21605.95</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -13141,28 +13141,28 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-Condenser -SB-PT</t>
+          <t>Audio Array-B0DXFPM4N2-Studio Monitor- SBV-CT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0DXFPM4N2</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>23409.33333333333</v>
+        <v>23825</v>
       </c>
       <c r="E14" t="n">
-        <v>87.33333333333333</v>
+        <v>317</v>
       </c>
       <c r="F14" t="n">
-        <v>1452.846666666667</v>
+        <v>1926.31</v>
       </c>
       <c r="G14" t="n">
-        <v>2287.29</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+          <t>Audio Array-Catch All-Condenser -SB-PT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -13183,19 +13183,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7349</v>
+        <v>70228</v>
       </c>
       <c r="E15" t="n">
-        <v>34.5</v>
+        <v>262</v>
       </c>
       <c r="F15" t="n">
-        <v>377.4632142857143</v>
+        <v>4358.54</v>
       </c>
       <c r="G15" t="n">
-        <v>1167.009642857143</v>
+        <v>6861.87</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4285714285714285</v>
+        <v>3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -13212,23 +13212,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E16" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F16" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G16" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -13245,23 +13245,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E17" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F17" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G17" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -13278,23 +13278,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E18" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F18" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G18" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -13311,23 +13311,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0B4G1PXWV</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E19" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F19" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G19" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -13344,23 +13344,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E20" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F20" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G20" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -13377,23 +13377,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E21" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F21" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G21" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -13410,23 +13410,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E22" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F22" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G22" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -13443,23 +13443,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0BLK8DNPD</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7349</v>
+        <v>14498</v>
       </c>
       <c r="E23" t="n">
-        <v>34.5</v>
+        <v>128</v>
       </c>
       <c r="F23" t="n">
-        <v>377.4632142857143</v>
+        <v>1896.908928571429</v>
       </c>
       <c r="G23" t="n">
-        <v>1167.009642857143</v>
+        <v>1372.946071428571</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4285714285714285</v>
+        <v>2</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -13476,23 +13476,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0BPLZ5CGV</t>
+          <t>B0BLK8DNPD</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E24" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F24" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G24" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -13509,23 +13509,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0BPLZ5CGV</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>7349</v>
+        <v>63909</v>
       </c>
       <c r="E25" t="n">
-        <v>34.5</v>
+        <v>337</v>
       </c>
       <c r="F25" t="n">
-        <v>377.4632142857143</v>
+        <v>3366.848928571429</v>
       </c>
       <c r="G25" t="n">
-        <v>1167.009642857143</v>
+        <v>18700.90607142857</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4285714285714285</v>
+        <v>5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -13542,23 +13542,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B0C539RBGL</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E26" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F26" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G26" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -13575,23 +13575,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0C539RBGL</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E27" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F27" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G27" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -13608,23 +13608,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E28" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F28" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G28" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -13641,23 +13641,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E29" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F29" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G29" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -13674,23 +13674,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>7349</v>
+        <v>7726</v>
       </c>
       <c r="E30" t="n">
-        <v>34.5</v>
+        <v>47</v>
       </c>
       <c r="F30" t="n">
-        <v>377.4632142857143</v>
+        <v>1189.458928571429</v>
       </c>
       <c r="G30" t="n">
-        <v>1167.009642857143</v>
+        <v>6542.436071428571</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4285714285714285</v>
+        <v>2</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -13707,23 +13707,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E31" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F31" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G31" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -13740,23 +13740,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E32" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F32" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G32" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H32" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -13773,23 +13773,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E33" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F33" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G33" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H33" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -13806,23 +13806,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0DFMLS8JG</t>
+          <t>B0CM6NVLT9</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>7349</v>
+        <v>25618</v>
       </c>
       <c r="E34" t="n">
-        <v>34.5</v>
+        <v>100</v>
       </c>
       <c r="F34" t="n">
-        <v>377.4632142857143</v>
+        <v>892.28</v>
       </c>
       <c r="G34" t="n">
-        <v>1167.009642857143</v>
+        <v>1355.08</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4285714285714285</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -13839,23 +13839,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DFMMTWLY</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E35" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F35" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G35" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H35" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -13872,23 +13872,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0DFMLS8JG</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E36" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F36" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G36" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -13905,23 +13905,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0DFMMTWLY</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E37" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F37" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G37" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H37" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -13938,23 +13938,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E38" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F38" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G38" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -13971,23 +13971,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0G2C2RCXN</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E39" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F39" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G39" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H39" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -14004,23 +14004,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E40" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F40" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G40" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -14037,23 +14037,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0G2C2RCXN</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E41" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F41" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G41" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -14070,23 +14070,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>7349</v>
+        <v>3761</v>
       </c>
       <c r="E42" t="n">
-        <v>34.5</v>
+        <v>14</v>
       </c>
       <c r="F42" t="n">
-        <v>377.4632142857143</v>
+        <v>128.9389285714286</v>
       </c>
       <c r="G42" t="n">
-        <v>1167.009642857143</v>
+        <v>188.1960714285714</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4285714285714285</v>
+        <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -14098,30 +14098,96 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B0G3Q59X8C</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>3761</v>
+      </c>
+      <c r="E43" t="n">
+        <v>14</v>
+      </c>
+      <c r="F43" t="n">
+        <v>128.9389285714286</v>
+      </c>
+      <c r="G43" t="n">
+        <v>188.1960714285714</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>B0G4DNF8RZ</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>3761</v>
+      </c>
+      <c r="E44" t="n">
+        <v>14</v>
+      </c>
+      <c r="F44" t="n">
+        <v>128.9389285714286</v>
+      </c>
+      <c r="G44" t="n">
+        <v>188.1960714285714</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>Ton_Condenser_TC-777_SBV_KT</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>B07WLWN2ZT</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D45" t="n">
         <v>158</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E45" t="n">
         <v>2</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F45" t="n">
         <v>79.59</v>
       </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="inlineStr">
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
         <is>
           <t>Audio Array</t>
         </is>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week17.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week17.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
